--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -62886,6 +62886,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1048</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>17.5499992370605</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -62917,7 +62917,7 @@
         <v>1048</v>
       </c>
       <c r="C2720" t="n">
-        <v>17.9500007629395</v>
+        <v>18.25</v>
       </c>
       <c r="D2720" t="n">
         <v>17.5499992370605</v>
@@ -62929,6 +62929,29 @@
         <v>18.25</v>
       </c>
       <c r="G2720" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>63</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>17.5499992370605</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="G2721" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -62940,7 +62940,7 @@
         <v>63</v>
       </c>
       <c r="C2721" t="n">
-        <v>18.1499996185303</v>
+        <v>18.25</v>
       </c>
       <c r="D2721" t="n">
         <v>17.5499992370605</v>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -62796,19 +62796,19 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="C2715" t="n">
-        <v>17.9500007629395</v>
+        <v>18.2000007629395</v>
       </c>
       <c r="D2715" t="n">
         <v>17.9500007629395</v>
       </c>
       <c r="E2715" t="n">
-        <v>17.9500007629395</v>
+        <v>18.2000007629395</v>
       </c>
       <c r="F2715" t="n">
         <v>17.9500007629395</v>
@@ -62819,16 +62819,16 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>179</v>
+        <v>0</v>
       </c>
       <c r="C2716" t="n">
         <v>17.9500007629395</v>
       </c>
       <c r="D2716" t="n">
-        <v>17.8999996185303</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="E2716" t="n">
         <v>17.9500007629395</v>
@@ -62842,16 +62842,16 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>0</v>
+        <v>179</v>
       </c>
       <c r="C2717" t="n">
         <v>17.9500007629395</v>
       </c>
       <c r="D2717" t="n">
-        <v>17.9500007629395</v>
+        <v>17.8999996185303</v>
       </c>
       <c r="E2717" t="n">
         <v>17.9500007629395</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="C2718" t="n">
-        <v>18.2999992370605</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="D2718" t="n">
         <v>17.9500007629395</v>
       </c>
       <c r="E2718" t="n">
-        <v>18.2000007629395</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="F2718" t="n">
-        <v>18.2999992370605</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,19 +62888,19 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="C2719" t="n">
         <v>18.2999992370605</v>
       </c>
       <c r="D2719" t="n">
-        <v>18.2999992370605</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="E2719" t="n">
-        <v>18.2999992370605</v>
+        <v>18.2000007629395</v>
       </c>
       <c r="F2719" t="n">
         <v>18.2999992370605</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1048</v>
+        <v>0</v>
       </c>
       <c r="C2720" t="n">
-        <v>18.25</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="D2720" t="n">
-        <v>17.5499992370605</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="E2720" t="n">
-        <v>17.9500007629395</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="F2720" t="n">
-        <v>18.25</v>
+        <v>18.2999992370605</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,10 +62934,10 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>63</v>
+        <v>1048</v>
       </c>
       <c r="C2721" t="n">
         <v>18.25</v>
@@ -62946,12 +62946,35 @@
         <v>17.5499992370605</v>
       </c>
       <c r="E2721" t="n">
-        <v>18.1499996185303</v>
+        <v>17.9500007629395</v>
       </c>
       <c r="F2721" t="n">
         <v>18.25</v>
       </c>
       <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>63</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>17.5499992370605</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>18.25</v>
+      </c>
+      <c r="G2722" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63047,6 +63047,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="G2726" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63116,6 +63116,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2729">
+      <c r="A2729" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2729" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2729" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="D2729" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="E2729" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2729" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="G2729" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2730">
+      <c r="A2730" s="1" t="n">
+        <v>46293.2916666667</v>
+      </c>
+      <c r="B2730" t="n">
+        <v>150</v>
+      </c>
+      <c r="C2730" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="D2730" t="n">
+        <v>17.8999996185303</v>
+      </c>
+      <c r="E2730" t="n">
+        <v>18.1000003814697</v>
+      </c>
+      <c r="F2730"/>
+      <c r="G2730" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63224,7 +63224,9 @@
       <c r="E2733" t="n">
         <v>18.2000007629395</v>
       </c>
-      <c r="F2733"/>
+      <c r="F2733" t="n">
+        <v>18.1499996185303</v>
+      </c>
       <c r="G2733" t="s">
         <v>7</v>
       </c>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63231,6 +63231,50 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2734">
+      <c r="A2734" s="1" t="n">
+        <v>46297.2916666667</v>
+      </c>
+      <c r="B2734" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2734" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="D2734" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="E2734" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2734" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="G2734" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2735">
+      <c r="A2735" s="1" t="n">
+        <v>46300.2916666667</v>
+      </c>
+      <c r="B2735" t="n">
+        <v>16</v>
+      </c>
+      <c r="C2735" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="D2735" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="E2735" t="n">
+        <v>17.6499996185303</v>
+      </c>
+      <c r="F2735"/>
+      <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63262,7 +63262,7 @@
         <v>16</v>
       </c>
       <c r="C2735" t="n">
-        <v>17.6499996185303</v>
+        <v>18.1499996185303</v>
       </c>
       <c r="D2735" t="n">
         <v>17.6499996185303</v>
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>17.6499996185303</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>18.1499996185303</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>514</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>18.6000003814697</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>17.8500003814697</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>18.1499996185303</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>18.1499996185303</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>18.2000007629395</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>20</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>18.5499992370605</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>18.5499992370605</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>18.5499992370605</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>18.5499992370605</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>36</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>18.3999996185303</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>17.9500007629395</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>17.9500007629395</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>29</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/TYA.MI.xlsx
+++ b/data/TYA.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>197</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>18.3500003814697</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>17.9500007629395</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>18.2999992370605</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
